--- a/xlsx/saude_teste.xlsx
+++ b/xlsx/saude_teste.xlsx
@@ -16,11 +16,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>loteId</t>
   </si>
   <si>
+    <t>brinco</t>
+  </si>
+  <si>
     <t>data</t>
   </si>
   <si>
@@ -48,6 +51,9 @@
     <t>FQ-2026-S01</t>
   </si>
   <si>
+    <t>FK-3002</t>
+  </si>
+  <si>
     <t>VACINA</t>
   </si>
   <si>
@@ -63,6 +69,9 @@
     <t xml:space="preserve">Dr. Silva</t>
   </si>
   <si>
+    <t>FK-3008</t>
+  </si>
+  <si>
     <t>VERMIFUGO</t>
   </si>
   <si>
@@ -76,6 +85,9 @@
   </si>
   <si>
     <t>FQ-2026-B01</t>
+  </si>
+  <si>
+    <t>FK-3015</t>
   </si>
   <si>
     <t>TRATAMENTO</t>
@@ -122,8 +134,11 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="164" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
@@ -626,21 +641,22 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col bestFit="1" min="1" max="1" width="11.890625"/>
-    <col bestFit="1" customWidth="1" min="2" max="2" width="10.83203125"/>
-    <col bestFit="1" min="3" max="3" width="13.12109375"/>
-    <col bestFit="1" min="4" max="4" width="12.6328125"/>
-    <col bestFit="1" min="5" max="5" width="8.47265625"/>
-    <col customWidth="1" min="6" max="6" width="18.57421875"/>
-    <col customWidth="1" min="7" max="7" width="19.421875"/>
-    <col bestFit="1" min="8" max="8" width="17.36328125"/>
-    <col bestFit="1" min="9" max="9" width="20.79296875"/>
+    <col min="2" max="2" width="11.890625"/>
+    <col bestFit="1" customWidth="1" min="3" max="3" width="10.83203125"/>
+    <col bestFit="1" min="4" max="4" width="13.12109375"/>
+    <col bestFit="1" min="5" max="5" width="12.6328125"/>
+    <col bestFit="1" min="6" max="6" width="8.47265625"/>
+    <col customWidth="1" min="7" max="7" width="18.57421875"/>
+    <col customWidth="1" min="8" max="8" width="19.421875"/>
+    <col bestFit="1" min="9" max="9" width="17.36328125"/>
+    <col bestFit="1" min="10" max="10" width="20.79296875"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -663,93 +679,105 @@
       </c>
       <c r="I1" t="s">
         <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="2" ht="14.25">
       <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="1">
+        <v>10</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="2">
         <v>46091</v>
       </c>
-      <c r="C2" t="s">
-        <v>10</v>
-      </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2">
         <v>21</v>
       </c>
-      <c r="H2" s="2">
+      <c r="I2" s="3">
         <v>45000</v>
       </c>
-      <c r="I2" t="s">
-        <v>14</v>
+      <c r="J2" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="3" ht="14.25">
       <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="1">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="2">
         <v>46093</v>
       </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
       <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3">
+        <v>28</v>
+      </c>
+      <c r="I3" s="3">
+        <v>12000</v>
+      </c>
+      <c r="J3" t="s">
         <v>16</v>
-      </c>
-      <c r="E3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3">
-        <v>28</v>
-      </c>
-      <c r="H3" s="2">
-        <v>12000</v>
-      </c>
-      <c r="I3" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="4" ht="14.25">
       <c r="A4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="1">
+        <v>22</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="2">
         <v>46096</v>
       </c>
-      <c r="C4" t="s">
-        <v>20</v>
-      </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4">
+        <v>26</v>
+      </c>
+      <c r="G4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4">
         <v>30</v>
       </c>
-      <c r="H4" s="2">
+      <c r="I4" s="3">
         <v>85000</v>
       </c>
-      <c r="I4" t="s">
-        <v>14</v>
+      <c r="J4" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
